--- a/parser/data/xlsx/evaluation.xlsx
+++ b/parser/data/xlsx/evaluation.xlsx
@@ -543,17 +543,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>eval_5c7bf57c759a</t>
+          <t>eval_eaded41753bd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T16:56:45.553656</t>
+          <t>2026-02-25T17:23:32.675565</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0a05cb32-2700-44d7-b6c8-e69700564f6f</t>
+          <t>393be70b-2760-4402-b968-a900df46a52e</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -568,16 +568,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>data_preprocessed_1_c24603f2_final</t>
+          <t>data_preprocessed_1_0b0ba787_final</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_c24603f2_final.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_0b0ba787_final.csv</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.203170100023272</v>
+        <v>1.326650300004985</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>

--- a/parser/data/xlsx/evaluation.xlsx
+++ b/parser/data/xlsx/evaluation.xlsx
@@ -543,17 +543,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>eval_eaded41753bd</t>
+          <t>eval_1582699343a9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T17:23:32.675565</t>
+          <t>2026-02-25T18:04:21.612403</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>393be70b-2760-4402-b968-a900df46a52e</t>
+          <t>d2991275-8bd1-4891-9a74-05fac8c1f674</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -568,16 +568,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>data_preprocessed_1_0b0ba787_final</t>
+          <t>data_preprocessed_1_7ee3ce34_final</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_0b0ba787_final.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_7ee3ce34_final.csv</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.326650300004985</v>
+        <v>1.267070799978683</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>

--- a/parser/data/xlsx/evaluation.xlsx
+++ b/parser/data/xlsx/evaluation.xlsx
@@ -423,7 +423,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="109" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="45" customWidth="1" min="10" max="10"/>
     <col width="45" customWidth="1" min="11" max="11"/>
@@ -543,17 +543,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>eval_1582699343a9</t>
+          <t>eval_5943e08e49af</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T18:04:21.612403</t>
+          <t>2026-02-26T13:48:53.632370</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>d2991275-8bd1-4891-9a74-05fac8c1f674</t>
+          <t>0cdce9cb-7efe-4ba2-b745-2071ff6b7348</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -568,16 +568,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>data_preprocessed_1_7ee3ce34_final</t>
+          <t>data_preprocessed_1_ca031a75_final</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_7ee3ce34_final.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_ca031a75_final.csv</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.267070799978683</v>
+        <v>1.609604400000535</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>

--- a/parser/data/xlsx/evaluation.xlsx
+++ b/parser/data/xlsx/evaluation.xlsx
@@ -421,9 +421,9 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="109" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="64" customWidth="1" min="6" max="6"/>
+    <col width="137" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="45" customWidth="1" min="10" max="10"/>
     <col width="45" customWidth="1" min="11" max="11"/>
@@ -543,17 +543,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>eval_5943e08e49af</t>
+          <t>eval_e768ad73085a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-26T13:48:53.632370</t>
+          <t>2026-02-26T14:46:13.816874</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0cdce9cb-7efe-4ba2-b745-2071ff6b7348</t>
+          <t>bb008549-d3df-465d-acd7-b232b9420c64</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -568,16 +568,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>data_preprocessed_1_ca031a75_final</t>
+          <t>7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348_final</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_ca031a75_final.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348_final.csv</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.609604400000535</v>
+        <v>1.502410600020085</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>

--- a/parser/data/xlsx/evaluation.xlsx
+++ b/parser/data/xlsx/evaluation.xlsx
@@ -543,17 +543,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>eval_e768ad73085a</t>
+          <t>eval_52cec615e232</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-26T14:46:13.816874</t>
+          <t>2026-02-26T14:55:28.234848</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bb008549-d3df-465d-acd7-b232b9420c64</t>
+          <t>3c8d9aba-e747-404c-93ba-1598590ce4e9</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -568,16 +568,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348_final</t>
+          <t>5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4_final</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348_final.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4_final.csv</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.502410600020085</v>
+        <v>1.578005200019106</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>

--- a/parser/data/xlsx/evaluation.xlsx
+++ b/parser/data/xlsx/evaluation.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:X4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -434,8 +434,12 @@
     <col width="36" customWidth="1" min="16" max="16"/>
     <col width="36" customWidth="1" min="17" max="17"/>
     <col width="32" customWidth="1" min="18" max="18"/>
-    <col width="45" customWidth="1" min="19" max="19"/>
-    <col width="49" customWidth="1" min="20" max="20"/>
+    <col width="68" customWidth="1" min="19" max="19"/>
+    <col width="74" customWidth="1" min="20" max="20"/>
+    <col width="31" customWidth="1" min="21" max="21"/>
+    <col width="35" customWidth="1" min="22" max="22"/>
+    <col width="36" customWidth="1" min="23" max="23"/>
+    <col width="48" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -539,6 +543,26 @@
           <t>retraining_analysis_llm_summary</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>metrics_raw_clustering_status</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>metrics_raw_clustering_n_clusters</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>metrics_raw_clustering_noise_ratio</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>metrics_raw_clustering_n_numeric_features_used</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -620,6 +644,146 @@
         <is>
           <t>Model performance stable. No retraining needed.</t>
         </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>eval_47bab0e39dcb</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-02-27T14:09:06.837474</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0c3f70a1-2e88-42a5-93b3-798bdc09e68d</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>kmeans</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>clustering</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>data_preprocessed_1_c13340b5_final</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_c13340b5_final.csv</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>17.13925120001659</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>unsupervised task does not use train-validation generalization gap</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Validation gap is not applicable for clustering runs (strategy=fit_all).</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>trained_full_dataset</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>12</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>eval_8f310e71ff90</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-02-27T14:13:48.377182</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>c3f5ac6e-72a6-4cfb-b346-80fda5315782</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>kmeans</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>clustering</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>42d1e5bfc1a9434c8980fd2b57f3f8d8_preprocessed_1_40ded763_final</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\42d1e5bfc1a9434c8980fd2b57f3f8d8_preprocessed_1_40ded763_final.csv</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>23.89120319997892</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>unsupervised task does not use train-validation generalization gap</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Validation gap is not applicable for clustering runs (strategy=fit_all).</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>trained_full_dataset</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>12</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
